--- a/claims_log.xlsx
+++ b/claims_log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Claims Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claims Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -868,6 +868,267 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>POL-2025-30044</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Deepak Rao</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 to 31-Dec-2025</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>01-Jul-2026</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Indiranagar, Bengaluru</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Two-wheeler collided with a parked vehicle, moderate damage to both.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Deepak Rao</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Owner of parked vehicle</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>deepak.rao@email.com, +91-9012345678</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Two-Wheeler</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>KA-03-XY-7788</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle Damage</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>photos.zip</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Standard Review</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Routed to Standard Review because estimated damage (₹25,000.00) is at or above the ₹25,000 threshold and no other flags were triggered.</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>regex_fallback</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MED5555</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>policyholder_name, effective_dates, date, time, location, description, claimant, third_parties, contact_details, asset_type, asset_id, estimated_damage, claim_type, attachments, initial_estimate</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Manual Review</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Routed to Manual Review because 15 mandatory field(s) are missing: policyholder_name, effective_dates, date, time, location, description, claimant, third_parties, contact_details, asset_type, asset_id, estimated_damage, claim_type, attachments, initial_estimate.</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>regex_fallback</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:07:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>POL-2025-30055</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sneha Reddy</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 to 31-Dec-2025</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>03-Jul-2026</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>HSR Layout, Bengaluru</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Cracked windshield from a stray stone on the highway.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Sneha Reddy</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>sneha.reddy@email.com, +91-9123400000</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>KA-04-CD-4455</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24999</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle Damage</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>photo.jpg</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>24999</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Fast-track</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Routed to Fast-track because estimated damage (₹24,999.00) is below the ₹25,000 threshold and no other flags were triggered.</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>regex_fallback</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:24:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
